--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.attributeSet.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.attributeSet.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -877,15 +877,68 @@
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
+      <c r="B16" t="n">
+        <v>9001</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>AutoChessCombat</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>AutoChess runtime combat attributes</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="F16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
+      <c r="G16" t="n">
+        <v>100</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>99999</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>99999</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="n"/>
